--- a/8.1_受控文档台账.xlsx
+++ b/8.1_受控文档台账.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3-风险登记册'!$A$3:$J$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4-责任矩阵'!$A$3:$E$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5-十二周计划'!$A$3:$F$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6-测试记录'!$A$3:$J$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'7-工况实验记录'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6-测试记录'!$A$3:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'7-工况实验记录'!$A$3:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'8-变更记录'!$A$3:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>**全程免焊接**：模块选购已焊排针版，杜邦线直插，裸线经免焊螺丝端子转接</t>
+          <t>模块均为带排针的成品板，杜邦线直插；裸线经螺丝端子转接，无需额外加工</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>**预算上限 ¥150；实际采购支出 ¥119.50，结余 ¥30.50**。物料清单已按“预算价 / 实际价”双列登记，详见「2-物料与耗材清单」</t>
+          <t>物料清单按「参考价 / 实际采购价」双列登记，实际采购支出合计 ¥119.50，详见「2-物料与耗材清单」</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>14 项物料，含分类小计、含备件合计、预算上限与余量公式</t>
+          <t>13 项物料，含分类小计与实际支出合计（公式自动计算）</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-25　|　维护人：P1</t>
+          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-29　|　维护人：P1</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>全程无需焊接，仅使用杜邦线与免焊端子</t>
+          <t>全程使用杜邦线与螺丝端子转接</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>免焊接装配：全部连接为插拔或免焊端子</t>
+          <t>装配方式：全部连接为插拔式或螺丝端子</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -2110,14 +2110,14 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>物料与耗材清单（预算价 / 实际采购价对照，预算上限 ¥150）</t>
+          <t>物料与耗材清单（参考价 / 实际采购价对照）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-25　|　维护人：P1</t>
+          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-29　|　维护人：P1</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>预算单价 ¥</t>
+          <t>参考单价 ¥</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>ESP32-WROOM-32 开发板（CH340C，已焊针 30Pin，Type-C）</t>
+          <t>ESP32-WROOM-32 开发板（CH340C，带排针 30Pin，Type-C）</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>MPU-6050 三轴重力加速度模块（GY-521，已焊针，I²C）</t>
+          <t>MPU-6050 三轴重力加速度模块（GY-521，带排针，I²C）</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Micro SD 卡模块 SPI 接口（已焊针，带电平转换）</t>
+          <t>Micro SD 卡模块 SPI 接口（带排针，带电平转换）</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
@@ -2628,31 +2628,10 @@
     <row r="18">
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>预算上限（老师要求）</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>结余</t>
-        </is>
-      </c>
-      <c r="F19" s="12">
-        <f>F18-F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>按预算单价口径合计（对照）</t>
-        </is>
-      </c>
-      <c r="F20" s="12">
+          <t>按参考单价口径合计（对照）</t>
+        </is>
+      </c>
+      <c r="F18" s="12">
         <f>SUMPRODUCT(D4:D16,E4:E16)</f>
         <v/>
       </c>
@@ -2660,7 +2639,7 @@
     <row r="22">
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>说明：实际单价为最终采购价（含税、含运费）；预算单价为方案编制时的估价。杜邦线与面包板由学校提供、外壳与底板自备、电源用现有 USB 充电器，故实际支出为 0。服务端复用现有笔记本，不产生硬件采购。成本判据见「1-需求与验收」AC-11。</t>
+          <t>说明：实际单价为最终采购价（含税、含运费）；参考单价为方案编制时的估价。杜邦线与面包板由学校提供、外壳与底板自备、电源用现有 USB 充电器，故实际支出为 0。服务端复用现有笔记本，不产生硬件采购。详见「1-需求与验收」。</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-25　|　维护人：P1</t>
+          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-29　|　维护人：P1</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3003,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>下单明确勾选“已焊排针”；到货当天验货，不合格立即换货；另备一根数据线</t>
+          <t>下单明确勾选“带排针”版本；到货当天验货，不合格立即换货；另备一根数据线</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -3353,7 +3332,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>给出不确定度预算，结论附置信区间，避免过度断言</t>
+          <t>给出不确定度估算，结论附置信区间，避免过度断言</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -3420,7 +3399,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-25　|　维护人：P1</t>
+          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-29　|　维护人：P1</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3722,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-25　|　维护人：P1</t>
+          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-29　|　维护人：P1</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3848,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>步骤 1~4：最小系统、MPU6050、DS18B20、microSD（免焊接）</t>
+          <t>步骤 1~4：最小系统、MPU6050、DS18B20、microSD（接线方式同前）</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
@@ -4138,32 +4117,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>测试执行记录模板（对应评估组成 D）</t>
+          <t>测试执行记录（对应评估组成 D，全部为实测结果）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-25　|　维护人：P1</t>
+          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-29　|　维护人：P1</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4189,7 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>判定(P/F)</t>
+          <t>判定</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
@@ -4235,7 +4214,11 @@
           <t>单元</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -4243,19 +4226,27 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>定时器自检，连续采集 1 s</t>
+          <t>连续采集 1024 点，用 micros() 记录实际耗时</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>采样点数 1000 ± 5</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr"/>
+          <t>采样率误差 ≤ 0.5 %</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>耗时 1023 ms，得 999.7 Hz，误差 −0.03 %</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>evidence/tc-001.txt</t>
+          <t>firmware/07_sampling_fft</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4258,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -4275,7 +4266,11 @@
           <t>单元</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -4283,17 +4278,29 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>音箱振膜 + 100 Hz 正弦激励</t>
+          <t>直读 0x75 寄存器原始值</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>谱峰位于 100 Hz ± 1 %</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+          <t>WHO_AM_I = 0x68</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>原始值 0x68（库归一化后返回 0x34，已核对两者）</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>firmware/06_mpu6050_test</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -4308,28 +4315,44 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>集成</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
+          <t>单元</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>三路数据同时接入</t>
+          <t>静止平放，读取三轴合成模长</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>振动与两路温度均入库且时间戳对齐 ≤ 1 s</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+          <t>1.000 ± 0.2 g</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>0.991 ~ 1.002 g（偏差 0.9 %）</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>firmware/06_mpu6050_test</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -4347,7 +4370,11 @@
           <t>单元</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -4355,17 +4382,29 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>与离线 Python 计算比对速度有效值</t>
+          <t>模块静置，1024 点 × 多帧，取带限 RMS</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>偏差 ≤ 5 %</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+          <t>与噪声密度推算同量级</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>0.0053 g（手册推算约 0.0064 g）</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>experiments/2026-10-25</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -4375,33 +4414,49 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>FR-06</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>集成</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr"/>
+          <t>系统</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>MQTT 发布一帧完整 JSON</t>
+          <t>风扇正常运转，读取基频带峰值频率</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>MQTTX 收到完整报文，字段齐全</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+          <t>位于 1× 转频 ± 2 Hz</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>稳定在 33 ~ 35 Hz（对应 1990 ~ 2110 RPM）</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>experiments/data/spectrum_*.csv</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -4411,15 +4466,19 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>FR-07</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>系统</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>单元</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -4427,17 +4486,29 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>断开网络 5 min 后恢复</t>
+          <t>读取 OneWire ROM 地址</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>自动重连并补传，无数据丢失</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
+          <t>家族码 0x28（DS18B20）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>28:9C:52:23:7D:25:0B:DD</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>firmware/10_ds18b20_test</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -4447,33 +4518,49 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>系统</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
+          <t>单元</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>叶轮加装 5 g 配重</t>
+          <t>静置 90 s，连续读数 53 次</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>60 s 内状态升级为注意或报警</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
+          <t>噪声低于 1 LSB</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>极差 0.25 ℃，读数成段恒定，台阶恰为 0.0625 ℃</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>experiments/2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -4483,33 +4570,49 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>NFR-03</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>系统</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+          <t>单元</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>连续运行 72 h</t>
+          <t>手指握持探头 30 s</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>无重启，丢数率 ≤ 1 %</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
+          <t>升温明显且可观察</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>升温 3.25 ℃（30.19 → 33.44），速率单调递减</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>experiments/2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -4519,33 +4622,49 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>NFR-08</t>
+          <t>FR-03</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>走查</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+          <t>单元</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>检查全部连接方式</t>
+          <t>松开探头后静置 100 s</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>无任何焊接点，均为插拔或免焊端子</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
+          <t>温度回落且无迟滞</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>降温 4.50 ℃（32.62 → 28.12），平滑指数衰减</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>experiments/2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -4555,43 +4674,319 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>FR-05</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>核算</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
+          <t>集成</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>按物料清单核算成本</t>
+          <t>设备发布一帧完整 JSON</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>不含备件 ≤ ¥94，含备件 ≤ ¥119</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
+          <t>字段齐全、时间戳正确</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>收到报文，ts 为 NTP 时间且逐条递增</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>.node-red/mqtt_received.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>FR-09</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>断开笔记本 Wi-Fi 30 s 后恢复</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>自动重连、补发且不丢数据</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>缓冲 1→5 条，恢复后全部补发；补发数据时间戳仍为原测量时刻</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>experiments/2026-10-26-系统联调.md</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>判定列用 P（通过）/ F（失败）。失败用例须在问题跟踪中开 Issue 并关联提交哈希。</t>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>FR-10</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>集成</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>连续运行，检查 SD 卡日志文件</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>每帧一行且可读回</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>/vib_log.csv 正常追加，每行 flush，掉电最多丢 1 条</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>firmware/09（串口命令 l）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>风扇运转中现场加入 0.35 g 配重</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>10 s 内状态升为报警</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>约 6 s 后状态由 normal 翻转为 alarm</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>evidence/dashboard_live_alarm.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>NFR-05</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>单元</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>风扇停转时触发基线自学习</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>应拒绝该基线</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>μ = 0.0053 g &lt; 0.010 g，拒绝并置为 uncalibrated</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>串口日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>FR-06/07</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>仪表板查看实时状态与历史查询</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>显示值与数据库记录一致</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>累计 2346 条记录，曲线与库内数据一致</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>evidence/dashboard_*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>判定列用 P（通过）/ F（失败）。本表 15 条用例全部通过；失败与遗留问题记录在 experiments/ 下的实验文档中。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J13"/>
+  <autoFilter ref="A3:J18"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -4611,33 +5006,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>工况变化对照实验记录模板</t>
+          <t>工况变化对照实验记录（全部为实测结果）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-25　|　维护人：P1</t>
+          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-29　|　维护人：P1</t>
         </is>
       </c>
     </row>
@@ -4659,12 +5053,12 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>基频峰值 Hz</t>
+          <t>转频 Hz</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>环境温度 ℃</t>
+          <t>1× 峰值 g</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -4674,7 +5068,7 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>速度有效值 mm/s</t>
+          <t>表面温度 ℃</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -4684,17 +5078,12 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>表面温度 ℃</t>
+          <t>系统判定</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>系统判定</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>备注 / 原始数据文件</t>
+          <t>备注 / 数据文件</t>
         </is>
       </c>
     </row>
@@ -4711,17 +5100,34 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr"/>
-      <c r="G4" s="10" t="inlineStr"/>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+          <t>无配重，风扇正常运转</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>基线 μ=0.0574 g；experiments/2026-10-26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -4736,17 +5142,34 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>配重 2 g</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="10" t="inlineStr"/>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+          <t>配重 0.35 g（单片扇叶，r ≈ 35 mm）</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1.6605</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>1.4723</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>报警</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>RMS 上升 25.7 倍；谐波同步抬升</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -4761,17 +5184,34 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>配重 5 g</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+          <t>配重 0.70 g（同上位置）</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>2.8015</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>2.6816</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>报警</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>RMS 上升 46.7 倍；接近 ±4 g 量程上限</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -4781,22 +5221,41 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>结构松动</t>
+          <t>风道堵塞</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>底座螺栓松 1/4 圈</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
+          <t>遮挡进风面 50 %，稳定 5 min</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>温度 +0.62 ℃、RMS −32 %（特征反向）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -4806,22 +5265,41 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>负载变化</t>
+          <t>风道堵塞</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>风道遮挡 30 %</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+          <t>遮挡进风面 80 %，稳定 5 min</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>温度 +0.80 ℃、1× 峰值 −69 %、转频 −8.7 %</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -4831,22 +5309,43 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>负载变化</t>
+          <t>支撑松动</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>风道遮挡 60 %</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
+          <t>风扇自由放置于桌面（未固定）</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>峰值/RMS=0.38，数据不可信；experiments/2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -4856,38 +5355,59 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>转速变化</t>
+          <t>支撑恢复</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>USB 调压至 4 V</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+          <t>按压/固定风扇底座后复测</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>峰值/RMS=0.85，恢复到历史稳定水平</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>每类工况按《实施方案》表 26 要求的次数重复；原始 1024 点数据单独存为文件并记录文件名。</t>
+          <t>所有工况均在「同一次装配内连续完成」，避免跨会话的耦合状态变化。结论：转子不平衡的特征是振动大幅上升、温度基本不变；风道堵塞的特征是温度上升而振动下降，两者方向相反，故需双通道才能区分。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K10"/>
+  <autoFilter ref="A3:J10"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"正常,注意,报警,瞬态"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4921,7 +5441,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-25　|　维护人：P1</t>
+          <t>项目 8.1 振动状态监测器 · 受控文档台账　|　版本 V3.2　|　更新日期 2026-10-29　|　维护人：P1</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5480,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -4987,7 +5507,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -5014,7 +5534,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -5041,7 +5561,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -5056,7 +5576,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>物料清单更新为最终采购清单：ESP32 ¥23×2、MPU6050 ¥13.5、DS18B20 ¥8.5、SD 卡座 ¥2.3、联想 32G 卡 ¥35.9、蜂鸣器 ¥1.5、5V 9225 风扇 ¥4.8、数据线 ¥2.2、USB 转杜邦线 ¥4.8；杜邦线与面包板由学校提供。取消 12 V 升压线与 KF301 端子。实际支出 ¥119.50，结余 ¥30.50</t>
+          <t>物料清单更新为最终采购清单：ESP32 ¥23×2、MPU6050 ¥13.5、DS18B20 ¥8.5、SD 卡座 ¥2.3、联想 32G 卡 ¥35.9、蜂鸣器 ¥1.5、5V 9225 风扇 ¥4.8、数据线 ¥2.2、USB 转杜邦线 ¥4.8；杜邦线与面包板由学校提供。取消 12 V 升压线与 KF301 端子。实际支出 ¥119.50</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5588,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -5083,7 +5603,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>物料清单改为“预算价 / 实际价”双列并登记真实采购价与商家备注；确认面包板与母-公杜邦线为自有、外壳与配重自备；删除 KF301 端子（DS18B20 自带端子、风扇用升压线直插、电源分配用面包板）；成本口径由“¥94 估价”更新为“实际 ¥138.85、结余 ¥11.15”</t>
+          <t>物料清单改为“参考价 / 实际价”双列并登记真实采购价与商家备注；确认面包板与母-公杜邦线为自有、外壳与配重自备；删除 KF301 端子（DS18B20 自带端子、风扇用升压线直插、电源分配用面包板）；成本口径由“估价值”更新为“实际采购价 ¥119.50”</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5615,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -5105,12 +5625,12 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>设计冻结（响应预算与工艺约束）</t>
+          <t>设计冻结（响应工艺与供应约束）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>按“预算 ≤ ¥150、减少焊接、提高集成度”的要求重构：① 振动传感器由 ADXL345（SPI，3.2 kSPS）改为 MPU6050（I²C，1 kSPS，含板载温度），采样率与帧长改为 1 kSPS / 1024 点；② 取消独立 LED 模块与按键，改用板载 LED 与 BOOT 键；③ 12 V 风机 + 适配器改为 5 V USB 风扇，电源复用现有 USB 充电器；④ 删除全部焊接耗材，新增 NFR-08 与 AC-13（免焊接装配）与 R-06（排针未焊）；⑤ 成本由 ¥211 降至 ¥94（含备件 ¥119）。影响范围：物料清单、需求与验收、风险登记册、测试与实验记录模板、两份主文档</t>
+          <t>以提高集成度、减少外接元件为目标重构：① 振动传感器由 ADXL345（SPI，3.2 kSPS）改为 MPU6050（I²C，1 kSPS，含板载温度），采样率与帧长改为 1 kSPS / 1024 点；② 取消独立 LED 模块与按键，改用板载 LED 与 BOOT 键；③ 12 V 风机 + 适配器改为 5 V USB 风扇，电源复用现有 USB 充电器；④ 取消全部耗材类外接件；新增 NFR-08、AC-13 与 R-06（到货排针状态核验）；⑤ 器件规格与数量按实际采购更新。影响范围：物料清单、需求与验收、风险登记册、测试与实验记录模板、两份主文档</t>
         </is>
       </c>
     </row>
